--- a/KURIKULUM2026_REVISI/009D_CPL_KETERAMPILAN_KHUSUS_SISTEKIN.xlsx
+++ b/KURIKULUM2026_REVISI/009D_CPL_KETERAMPILAN_KHUSUS_SISTEKIN.xlsx
@@ -2174,7 +2174,7 @@
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Laporan Analisis Kebutuhan Sistem Cerdas (STI-307 / STI-624).</t>
+          <t>Laporan Analisis Kebutuhan Sistem Cerdas (STI-307 / STI-726).</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Repositori Kode Sumber dan Prototipe Aplikasi Cerdas (STI-624).</t>
+          <t>Repositori Kode Sumber dan Prototipe Aplikasi Cerdas (STI-726).</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Model ML terlatih dengan evaluasi Confusion Matrix / F1-Score (STI-413 / STI-626).</t>
+          <t>Model ML terlatih dengan evaluasi Confusion Matrix / F1-Score (STI-413 / STI-726).</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Laporan Konfigurasi Keamanan Jaringan (STI-626 / STB-501).</t>
+          <t>Laporan Konfigurasi Keamanan Jaringan (STI-726 / STB-501).</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Laporan Hasil Audit Keamanan &amp; Uji Penetrasi (STI-626 / STB-501).</t>
+          <t>Laporan Hasil Audit Keamanan &amp; Uji Penetrasi (STI-726 / STB-501).</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Aplikasi Full-Stack Web di React/Vue/NodeJS/Go (STI-311 / STI-416 / STI-627).</t>
+          <t>Aplikasi Full-Stack Web di React/Vue/NodeJS/Go (STI-311 / STI-416 / STI-727).</t>
         </is>
       </c>
     </row>
